--- a/templates/Marks_template.xlsx
+++ b/templates/Marks_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Pro_Final\Final after github\c_p_m_Bvm-Profile\Campus_Placement_Management_System-master\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Pro_Final\c_p_m_new\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E6589F2-7108-4A32-9AC0-9984C147FFB5}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6323F5A6-5333-47B8-9806-B832E31A5A81}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{F29DF2A4-9382-4D8E-8CF6-0BEEDE8DF30F}"/>
   </bookViews>
@@ -30,9 +30,6 @@
     <t>id</t>
   </si>
   <si>
-    <t>username</t>
-  </si>
-  <si>
     <t>sem_1</t>
   </si>
   <si>
@@ -69,10 +66,13 @@
     <t>fourth_year</t>
   </si>
   <si>
-    <t>18IT402</t>
-  </si>
-  <si>
-    <t>18IT403</t>
+    <t>id_no</t>
+  </si>
+  <si>
+    <t>18ME402</t>
+  </si>
+  <si>
+    <t>18ME403</t>
   </si>
 </sst>
 </file>
@@ -432,43 +432,43 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
